--- a/reports/توقعات_المدفوعات_للبنك.xlsx
+++ b/reports/توقعات_المدفوعات_للبنك.xlsx
@@ -80,7 +80,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00F3EFEA"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,16 +90,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EFEA"/>
+        <fgColor rgb="00E4F2E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E4F2E7"/>
+        <fgColor rgb="00E7F0FA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -143,6 +143,17 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D7D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D7D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="00D9D7D3"/>
       </right>
@@ -158,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -172,20 +183,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -195,13 +210,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -574,20 +589,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E22"/>
+  <dimension ref="B2:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>درب — توقعات المبيعات وعدد العمليات (لبوابة الدفع)</t>
+          <t>درب — توقعات مبيعات التطبيق على كل المحطات (لبوابة الدفع)</t>
         </is>
       </c>
     </row>
@@ -601,197 +617,294 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>① المدخلات (توقعاتك)</t>
+          <t>① الثوابت</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>عدد العملاء النشطين المتوقع (السنة 1)</t>
+          <t>متوسط مبيعات المحطة / شهر (وقود+خدمات) ﷼</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>60000</v>
+        <v>200000</v>
       </c>
       <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>عدد عمليات الشحن للعميل / شهر</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>2</v>
+          <t>حصة مدى من القيمة</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>0.75</v>
       </c>
       <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>متوسط مبلغ الشحنة الواحدة (﷼)</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>200</v>
+          <t>متوسط قيمة عملية مدى (﷼)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>120</v>
       </c>
       <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>حصة مدى من إجمالي القيمة</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0.75</v>
+          <t>متوسط قيمة عملية فيزا (﷼)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>180</v>
       </c>
       <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>متوسط قيمة عملية مدى (﷼)</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>180</v>
-      </c>
-      <c r="D10" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>متوسط قيمة عملية فيزا (﷼)</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>260</v>
-      </c>
-      <c r="D11" s="6" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>② سيناريوهات النمو (3 سنوات)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>حصة فيزا (تُحسب تلقائياً)</t>
-        </is>
-      </c>
-      <c r="C12" s="10">
-        <f>1-C9</f>
-        <v/>
-      </c>
-      <c r="D12" s="6" t="n"/>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>السنة 1</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>السنة 2</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>السنة 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>عدد المحطات</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="10" t="n">
+        <v>173</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>② إجمالي المبيعات السنوية المتوقعة</t>
-        </is>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>نسبة المبيعات عبر التطبيق</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>إجمالي الشحن السنوي (﷼)</t>
-        </is>
-      </c>
-      <c r="C15" s="12">
-        <f>C6*C7*12*C8</f>
-        <v/>
-      </c>
-      <c r="D15" s="6" t="n"/>
+          <t>مبيعات المحطات السنوية (﷼)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="12">
+        <f>D13*C6*12</f>
+        <v/>
+      </c>
+      <c r="E15" s="12">
+        <f>E13*C6*12</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>F13*C6*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>مبيعات التطبيق السنوية (﷼)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="14">
+        <f>D13*C6*12*D14</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>E13*C6*12*E14</f>
+        <v/>
+      </c>
+      <c r="F16" s="14">
+        <f>F13*C6*12*F14</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>③ الأرقام المطلوبة للبنك</t>
-        </is>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>— منها مدى (﷼)</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="16">
+        <f>D16*C7</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
+        <f>E16*C7</f>
+        <v/>
+      </c>
+      <c r="F17" s="16">
+        <f>F16*C7</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>البند</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>مدى</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>فيزا</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>— منها فيزا (﷼)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="16">
+        <f>D16*(1-C7)</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>E16*(1-C7)</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>F16*(1-C7)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>المبيعات السنوية (﷼)</t>
-        </is>
-      </c>
-      <c r="C19" s="15">
-        <f>C15*C9</f>
-        <v/>
-      </c>
-      <c r="D19" s="15">
-        <f>C15*(1-C9)</f>
-        <v/>
-      </c>
-      <c r="E19" s="15">
-        <f>C15</f>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>عدد عمليات مدى</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="18">
+        <f>(D16*C7)/C8</f>
+        <v/>
+      </c>
+      <c r="E19" s="18">
+        <f>(E16*C7)/C8</f>
+        <v/>
+      </c>
+      <c r="F19" s="18">
+        <f>(F16*C7)/C8</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>عدد العمليات السنوية</t>
-        </is>
-      </c>
-      <c r="C20" s="16">
-        <f>(C15*C9)/C10</f>
-        <v/>
-      </c>
-      <c r="D20" s="16">
-        <f>(C15*(1-C9))/C11</f>
-        <v/>
-      </c>
-      <c r="E20" s="16">
-        <f>C20+D20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>ملاحظة: مدى أرخص رسوماً (شحن المحفظة ~1.5 ﷼ ثابت)؛ وجّه الشحن لمدى. الأرقام توقعية تُضبط بحجمك الفعلي.</t>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>عدد عمليات فيزا</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="18">
+        <f>(D16*(1-C7))/C9</f>
+        <v/>
+      </c>
+      <c r="E20" s="18">
+        <f>(E16*(1-C7))/C9</f>
+        <v/>
+      </c>
+      <c r="F20" s="18">
+        <f>(F16*(1-C7))/C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>إجمالي العمليات</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="18">
+        <f>D19+D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="18">
+        <f>E19+E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="18">
+        <f>F19+F20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>الأصفر = مُدخلات تعدّلينها (محطات + نسبة اعتماد لكل سنة). الباقي يُحسب تلقائياً. مدى أرخص رسوماً — وجّه الدفع لمدى.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B2:D2"/>
+  <mergeCells count="19">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/توقعات_المدفوعات_للبنك.xlsx
+++ b/reports/توقعات_المدفوعات_للبنك.xlsx
@@ -711,13 +711,13 @@
       </c>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="10" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14">

--- a/reports/توقعات_المدفوعات_للبنك.xlsx
+++ b/reports/توقعات_المدفوعات_للبنك.xlsx
@@ -624,11 +624,11 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>متوسط مبيعات المحطة / شهر (وقود+خدمات) ﷼</t>
+          <t>متوسط مبيعات المحطة / شهر ﷼ (فعلي Q2: ~1.24م للمشغّلة)</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>200000</v>
+        <v>1240000</v>
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>

--- a/reports/توقعات_المدفوعات_للبنك.xlsx
+++ b/reports/توقعات_المدفوعات_للبنك.xlsx
@@ -183,12 +183,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>أرقام توقعية · عدّل الأصفر فقط</t>
+          <t>مبنية على مبيعات المحطة الفعلية (تقرير Q2 2026) · افتراضات خبير معتمدة</t>
         </is>
       </c>
     </row>
@@ -624,11 +624,11 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>متوسط مبيعات المحطة / شهر ﷼ (فعلي Q2: ~1.24م للمشغّلة)</t>
+          <t>حصة مدى من القيمة</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1240000</v>
+        <v>0.75</v>
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
@@ -637,11 +637,11 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>حصة مدى من القيمة</t>
+          <t>متوسط قيمة عملية مدى (﷼)</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.75</v>
+        <v>120</v>
       </c>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
@@ -650,74 +650,78 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>متوسط قيمة عملية مدى (﷼)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>120</v>
+          <t>متوسط قيمة عملية فيزا (﷼)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>180</v>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="7" t="n"/>
     </row>
-    <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>متوسط قيمة عملية فيزا (﷼)</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>180</v>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="7" t="n"/>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>② سيناريوهات النمو (3 سنوات)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>② سيناريوهات النمو (3 سنوات)</t>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>المُدخلات</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>السنة 1</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>السنة 2</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>السنة 3</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>البند</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>عدد المحطات</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>السنة 1</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>السنة 2</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>السنة 3</t>
-        </is>
+      <c r="D12" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>عدد المحطات</t>
+          <t>متوسط مبيعات المحطة / شهر (﷼)</t>
         </is>
       </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>350</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>500</v>
+      <c r="D13" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>850000</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>750000</v>
       </c>
     </row>
     <row r="14">
@@ -727,14 +731,14 @@
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>0.7</v>
+      <c r="D14" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -745,15 +749,15 @@
       </c>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="12">
-        <f>D13*C6*12</f>
+        <f>D12*D13*12</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>E13*C6*12</f>
+        <f>E12*E13*12</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>F13*C6*12</f>
+        <f>F12*F13*12</f>
         <v/>
       </c>
     </row>
@@ -765,15 +769,15 @@
       </c>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="14">
-        <f>D13*C6*12*D14</f>
+        <f>D12*D13*12*D14</f>
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>E13*C6*12*E14</f>
+        <f>E12*E13*12*E14</f>
         <v/>
       </c>
       <c r="F16" s="14">
-        <f>F13*C6*12*F14</f>
+        <f>F12*F13*12*F14</f>
         <v/>
       </c>
     </row>
@@ -785,15 +789,15 @@
       </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="16">
-        <f>D16*C7</f>
+        <f>D16*C6</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>E16*C7</f>
+        <f>E16*C6</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>F16*C7</f>
+        <f>F16*C6</f>
         <v/>
       </c>
     </row>
@@ -805,15 +809,15 @@
       </c>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="16">
-        <f>D16*(1-C7)</f>
+        <f>D16*(1-C6)</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>E16*(1-C7)</f>
+        <f>E16*(1-C6)</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>F16*(1-C7)</f>
+        <f>F16*(1-C6)</f>
         <v/>
       </c>
     </row>
@@ -825,15 +829,15 @@
       </c>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="18">
-        <f>(D16*C7)/C8</f>
+        <f>(D16*C6)/C7</f>
         <v/>
       </c>
       <c r="E19" s="18">
-        <f>(E16*C7)/C8</f>
+        <f>(E16*C6)/C7</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>(F16*C7)/C8</f>
+        <f>(F16*C6)/C7</f>
         <v/>
       </c>
     </row>
@@ -845,15 +849,15 @@
       </c>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="18">
-        <f>(D16*(1-C7))/C9</f>
+        <f>(D16*(1-C6))/C8</f>
         <v/>
       </c>
       <c r="E20" s="18">
-        <f>(E16*(1-C7))/C9</f>
+        <f>(E16*(1-C6))/C8</f>
         <v/>
       </c>
       <c r="F20" s="18">
-        <f>(F16*(1-C7))/C9</f>
+        <f>(F16*(1-C6))/C8</f>
         <v/>
       </c>
     </row>
@@ -880,7 +884,7 @@
     <row r="23">
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>الأصفر = مُدخلات تعدّلينها (محطات + نسبة اعتماد لكل سنة). الباقي يُحسب تلقائياً. مدى أرخص رسوماً — وجّه الدفع لمدى.</t>
+          <t>الافتراضات (خبير): مبيعات المحطة تتناقص مع التوسّع (إضافة محطات أصغر)؛ نسبة الدفع عبر التطبيق تنمو تدريجياً. المصدر: تقرير Q2 2026 (~1.24م للمحطات المشغّلة الكبرى).</t>
         </is>
       </c>
     </row>
@@ -894,14 +898,14 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="C9:F9"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B5:F5"/>

--- a/reports/توقعات_المدفوعات_للبنك.xlsx
+++ b/reports/توقعات_المدفوعات_للبنك.xlsx
@@ -46,12 +46,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
       <color rgb="0026262A"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
       <color rgb="0026262A"/>
       <sz val="11"/>
     </font>
@@ -75,12 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4CC"/>
+        <fgColor rgb="00F3EFEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EFEA"/>
+        <fgColor rgb="00FFF4CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -99,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -143,17 +143,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D7D3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D7D3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="00D9D7D3"/>
       </right>
@@ -169,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -180,45 +169,44 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -589,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F23"/>
+  <dimension ref="B2:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -617,298 +605,248 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>① الثوابت</t>
+          <t>سيناريوهات النمو (3 سنوات)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>حصة مدى من القيمة</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="n"/>
+          <t>المُدخلات</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>السنة 1</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>السنة 2</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>السنة 3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>متوسط قيمة عملية مدى (﷼)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>عدد المحطات</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>متوسط قيمة عملية فيزا (﷼)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>180</v>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="n"/>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>متوسط مبيعات المحطة / شهر (﷼)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>850000</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>نسبة المبيعات عبر التطبيق</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>② سيناريوهات النمو (3 سنوات)</t>
-        </is>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>مبيعات المحطات السنوية (﷼)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="11">
+        <f>D7*D8*12</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>E7*E8*12</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>F7*F8*12</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>المُدخلات</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>السنة 1</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>السنة 2</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>السنة 3</t>
-        </is>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>مبيعات التطبيق السنوية (﷼)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="13">
+        <f>D7*D8*12*D9</f>
+        <v/>
+      </c>
+      <c r="E11" s="13">
+        <f>E7*E8*12*E9</f>
+        <v/>
+      </c>
+      <c r="F11" s="13">
+        <f>F7*F8*12*F9</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>عدد المحطات</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>350</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>500</v>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>— منها مدى (﷼)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="15">
+        <f>D11*0.75</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
+        <f>E11*0.75</f>
+        <v/>
+      </c>
+      <c r="F12" s="15">
+        <f>F11*0.75</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>متوسط مبيعات المحطة / شهر (﷼)</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>750000</v>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>— منها فيزا (﷼)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="15">
+        <f>D11*0.25</f>
+        <v/>
+      </c>
+      <c r="E13" s="15">
+        <f>E11*0.25</f>
+        <v/>
+      </c>
+      <c r="F13" s="15">
+        <f>F11*0.25</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>نسبة المبيعات عبر التطبيق</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.6</v>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>عدد عمليات مدى</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="17">
+        <f>(D11*0.75)/120</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>(E11*0.75)/120</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>(F11*0.75)/120</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>مبيعات المحطات السنوية (﷼)</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="12">
-        <f>D12*D13*12</f>
-        <v/>
-      </c>
-      <c r="E15" s="12">
-        <f>E12*E13*12</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
-        <f>F12*F13*12</f>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>عدد عمليات فيزا</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="17">
+        <f>(D11*0.25)/180</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>(E11*0.25)/180</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>(F11*0.25)/180</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>مبيعات التطبيق السنوية (﷼)</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="14">
-        <f>D12*D13*12*D14</f>
-        <v/>
-      </c>
-      <c r="E16" s="14">
-        <f>E12*E13*12*E14</f>
-        <v/>
-      </c>
-      <c r="F16" s="14">
-        <f>F12*F13*12*F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>— منها مدى (﷼)</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="16">
-        <f>D16*C6</f>
-        <v/>
-      </c>
-      <c r="E17" s="16">
-        <f>E16*C6</f>
-        <v/>
-      </c>
-      <c r="F17" s="16">
-        <f>F16*C6</f>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>إجمالي العمليات</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="17">
+        <f>D14+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>E14+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>F14+F15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>— منها فيزا (﷼)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="16">
-        <f>D16*(1-C6)</f>
-        <v/>
-      </c>
-      <c r="E18" s="16">
-        <f>E16*(1-C6)</f>
-        <v/>
-      </c>
-      <c r="F18" s="16">
-        <f>F16*(1-C6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>عدد عمليات مدى</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="18">
-        <f>(D16*C6)/C7</f>
-        <v/>
-      </c>
-      <c r="E19" s="18">
-        <f>(E16*C6)/C7</f>
-        <v/>
-      </c>
-      <c r="F19" s="18">
-        <f>(F16*C6)/C7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>عدد عمليات فيزا</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="18">
-        <f>(D16*(1-C6))/C8</f>
-        <v/>
-      </c>
-      <c r="E20" s="18">
-        <f>(E16*(1-C6))/C8</f>
-        <v/>
-      </c>
-      <c r="F20" s="18">
-        <f>(F16*(1-C6))/C8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>إجمالي العمليات</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="18">
-        <f>D19+D20</f>
-        <v/>
-      </c>
-      <c r="E21" s="18">
-        <f>E19+E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="18">
-        <f>F19+F20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>الافتراضات (خبير): مبيعات المحطة تتناقص مع التوسّع (إضافة محطات أصغر)؛ نسبة الدفع عبر التطبيق تنمو تدريجياً. المصدر: تقرير Q2 2026 (~1.24م للمحطات المشغّلة الكبرى).</t>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>الأصفر = مُدخلات قابلة للتعديل. الافتراضات الثابتة: مدى 75% من القيمة · متوسط تذكرة مدى 120 ﷼ / فيزا 180 ﷼ (مدمجة في المعادلات). المصدر: تقرير Q2 2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="15">
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
